--- a/templates/oefen/oefen_grondwater_template_full.xlsx
+++ b/templates/oefen/oefen_grondwater_template_full.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17707" uniqueCount="3324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17711" uniqueCount="3326">
   <si>
     <t>identificatie</t>
   </si>
@@ -9603,6 +9603,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -9963,13 +9969,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:51:44.028294</t>
+    <t>2026-05-06 16:21:28.670708</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>
@@ -11186,7 +11192,7 @@
 </file>
 
 <file path=xl/tables/table95.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="95" name="Table95" displayName="Table95" ref="GG3:GH12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="95" name="Table95" displayName="Table95" ref="GG3:GH14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -11718,7 +11724,7 @@
       <c r="FY1" s="1"/>
       <c r="FZ1" s="1"/>
       <c r="GA1" s="1" t="s">
-        <v>3238</v>
+        <v>3240</v>
       </c>
       <c r="GB1" s="1"/>
       <c r="GC1" s="1"/>
@@ -11760,7 +11766,7 @@
       <c r="HK1" s="1"/>
       <c r="HL1" s="1"/>
       <c r="HM1" s="1" t="s">
-        <v>3311</v>
+        <v>3313</v>
       </c>
       <c r="HN1" s="1"/>
     </row>
@@ -12158,15 +12164,15 @@
       </c>
       <c r="GN2" s="1"/>
       <c r="GO2" s="1" t="s">
-        <v>3239</v>
+        <v>3241</v>
       </c>
       <c r="GP2" s="1"/>
       <c r="GQ2" s="1" t="s">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="GR2" s="1"/>
       <c r="GS2" s="1" t="s">
-        <v>3263</v>
+        <v>3265</v>
       </c>
       <c r="GT2" s="1"/>
       <c r="GU2" s="1" t="s">
@@ -12194,11 +12200,11 @@
       </c>
       <c r="HF2" s="1"/>
       <c r="HG2" s="1" t="s">
-        <v>3292</v>
+        <v>3294</v>
       </c>
       <c r="HH2" s="1"/>
       <c r="HI2" s="1" t="s">
-        <v>3295</v>
+        <v>3297</v>
       </c>
       <c r="HJ2" s="1"/>
       <c r="HK2" s="1" t="s">
@@ -13450,13 +13456,13 @@
         <v>212</v>
       </c>
       <c r="GI4" s="2" t="s">
-        <v>3198</v>
+        <v>3200</v>
       </c>
       <c r="GJ4" t="s">
         <v>212</v>
       </c>
       <c r="GK4" s="2" t="s">
-        <v>3235</v>
+        <v>3237</v>
       </c>
       <c r="GL4" t="s">
         <v>212</v>
@@ -13510,7 +13516,7 @@
         <v>212</v>
       </c>
       <c r="HC4" s="2" t="s">
-        <v>3299</v>
+        <v>3301</v>
       </c>
       <c r="HD4" t="s">
         <v>212</v>
@@ -14118,13 +14124,13 @@
         <v>212</v>
       </c>
       <c r="GI5" s="2" t="s">
-        <v>3199</v>
+        <v>3201</v>
       </c>
       <c r="GJ5" t="s">
         <v>212</v>
       </c>
       <c r="GK5" s="2" t="s">
-        <v>3236</v>
+        <v>3238</v>
       </c>
       <c r="GL5" t="s">
         <v>212</v>
@@ -14178,7 +14184,7 @@
         <v>212</v>
       </c>
       <c r="HC5" s="2" t="s">
-        <v>3300</v>
+        <v>3302</v>
       </c>
       <c r="HD5" t="s">
         <v>212</v>
@@ -14756,13 +14762,13 @@
         <v>212</v>
       </c>
       <c r="GI6" s="2" t="s">
-        <v>3200</v>
+        <v>3202</v>
       </c>
       <c r="GJ6" t="s">
         <v>212</v>
       </c>
       <c r="GK6" s="2" t="s">
-        <v>3237</v>
+        <v>3239</v>
       </c>
       <c r="GL6" t="s">
         <v>212</v>
@@ -14816,7 +14822,7 @@
         <v>212</v>
       </c>
       <c r="HC6" s="2" t="s">
-        <v>3301</v>
+        <v>3303</v>
       </c>
       <c r="HD6" t="s">
         <v>212</v>
@@ -15268,7 +15274,7 @@
         <v>212</v>
       </c>
       <c r="GI7" s="2" t="s">
-        <v>3201</v>
+        <v>3203</v>
       </c>
       <c r="GJ7" t="s">
         <v>212</v>
@@ -15732,7 +15738,7 @@
         <v>212</v>
       </c>
       <c r="GI8" s="2" t="s">
-        <v>3202</v>
+        <v>3204</v>
       </c>
       <c r="GJ8" t="s">
         <v>212</v>
@@ -16160,7 +16166,7 @@
         <v>212</v>
       </c>
       <c r="GI9" s="2" t="s">
-        <v>3203</v>
+        <v>3205</v>
       </c>
       <c r="GJ9" t="s">
         <v>212</v>
@@ -16564,7 +16570,7 @@
         <v>212</v>
       </c>
       <c r="GI10" s="2" t="s">
-        <v>3204</v>
+        <v>3206</v>
       </c>
       <c r="GJ10" t="s">
         <v>212</v>
@@ -16944,7 +16950,7 @@
         <v>212</v>
       </c>
       <c r="GI11" s="2" t="s">
-        <v>3205</v>
+        <v>3207</v>
       </c>
       <c r="GJ11" t="s">
         <v>212</v>
@@ -17300,7 +17306,7 @@
         <v>212</v>
       </c>
       <c r="GI12" s="2" t="s">
-        <v>3206</v>
+        <v>3208</v>
       </c>
       <c r="GJ12" t="s">
         <v>212</v>
@@ -17637,8 +17643,14 @@
       <c r="GF13" t="s">
         <v>212</v>
       </c>
+      <c r="GG13" s="2" t="s">
+        <v>3198</v>
+      </c>
+      <c r="GH13" t="s">
+        <v>212</v>
+      </c>
       <c r="GI13" s="2" t="s">
-        <v>3207</v>
+        <v>3209</v>
       </c>
       <c r="GJ13" t="s">
         <v>212</v>
@@ -17969,8 +17981,14 @@
       <c r="GF14" t="s">
         <v>212</v>
       </c>
+      <c r="GG14" s="2" t="s">
+        <v>3199</v>
+      </c>
+      <c r="GH14" t="s">
+        <v>212</v>
+      </c>
       <c r="GI14" s="2" t="s">
-        <v>3208</v>
+        <v>3210</v>
       </c>
       <c r="GJ14" t="s">
         <v>212</v>
@@ -18284,7 +18302,7 @@
         <v>212</v>
       </c>
       <c r="GI15" s="2" t="s">
-        <v>3209</v>
+        <v>3211</v>
       </c>
       <c r="GJ15" t="s">
         <v>212</v>
@@ -18598,7 +18616,7 @@
         <v>212</v>
       </c>
       <c r="GI16" s="2" t="s">
-        <v>3210</v>
+        <v>3212</v>
       </c>
       <c r="GJ16" t="s">
         <v>212</v>
@@ -18906,7 +18924,7 @@
         <v>212</v>
       </c>
       <c r="GI17" s="2" t="s">
-        <v>3211</v>
+        <v>3213</v>
       </c>
       <c r="GJ17" t="s">
         <v>212</v>
@@ -19178,7 +19196,7 @@
         <v>212</v>
       </c>
       <c r="GI18" s="2" t="s">
-        <v>3212</v>
+        <v>3214</v>
       </c>
       <c r="GJ18" t="s">
         <v>212</v>
@@ -19438,7 +19456,7 @@
         <v>212</v>
       </c>
       <c r="GI19" s="2" t="s">
-        <v>3213</v>
+        <v>3215</v>
       </c>
       <c r="GJ19" t="s">
         <v>212</v>
@@ -19692,7 +19710,7 @@
         <v>212</v>
       </c>
       <c r="GI20" s="2" t="s">
-        <v>3214</v>
+        <v>3216</v>
       </c>
       <c r="GJ20" t="s">
         <v>212</v>
@@ -19910,7 +19928,7 @@
         <v>212</v>
       </c>
       <c r="GI21" s="2" t="s">
-        <v>3215</v>
+        <v>3217</v>
       </c>
       <c r="GJ21" t="s">
         <v>212</v>
@@ -20128,7 +20146,7 @@
         <v>212</v>
       </c>
       <c r="GI22" s="2" t="s">
-        <v>3216</v>
+        <v>3218</v>
       </c>
       <c r="GJ22" t="s">
         <v>212</v>
@@ -20346,7 +20364,7 @@
         <v>212</v>
       </c>
       <c r="GI23" s="2" t="s">
-        <v>3217</v>
+        <v>3219</v>
       </c>
       <c r="GJ23" t="s">
         <v>212</v>
@@ -20546,7 +20564,7 @@
         <v>212</v>
       </c>
       <c r="GI24" s="2" t="s">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="GJ24" t="s">
         <v>212</v>
@@ -20746,7 +20764,7 @@
         <v>212</v>
       </c>
       <c r="GI25" s="2" t="s">
-        <v>3219</v>
+        <v>3221</v>
       </c>
       <c r="GJ25" t="s">
         <v>212</v>
@@ -20940,7 +20958,7 @@
         <v>212</v>
       </c>
       <c r="GI26" s="2" t="s">
-        <v>3220</v>
+        <v>3222</v>
       </c>
       <c r="GJ26" t="s">
         <v>212</v>
@@ -21128,7 +21146,7 @@
         <v>212</v>
       </c>
       <c r="GI27" s="2" t="s">
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="GJ27" t="s">
         <v>212</v>
@@ -21310,7 +21328,7 @@
         <v>212</v>
       </c>
       <c r="GI28" s="2" t="s">
-        <v>3222</v>
+        <v>3224</v>
       </c>
       <c r="GJ28" t="s">
         <v>212</v>
@@ -21492,7 +21510,7 @@
         <v>212</v>
       </c>
       <c r="GI29" s="2" t="s">
-        <v>3223</v>
+        <v>3225</v>
       </c>
       <c r="GJ29" t="s">
         <v>212</v>
@@ -21668,7 +21686,7 @@
         <v>212</v>
       </c>
       <c r="GI30" s="2" t="s">
-        <v>3224</v>
+        <v>3226</v>
       </c>
       <c r="GJ30" t="s">
         <v>212</v>
@@ -21844,7 +21862,7 @@
         <v>212</v>
       </c>
       <c r="GI31" s="2" t="s">
-        <v>3225</v>
+        <v>3227</v>
       </c>
       <c r="GJ31" t="s">
         <v>212</v>
@@ -22014,7 +22032,7 @@
         <v>212</v>
       </c>
       <c r="GI32" s="2" t="s">
-        <v>3226</v>
+        <v>3228</v>
       </c>
       <c r="GJ32" t="s">
         <v>212</v>
@@ -22184,7 +22202,7 @@
         <v>212</v>
       </c>
       <c r="GI33" s="2" t="s">
-        <v>3227</v>
+        <v>3229</v>
       </c>
       <c r="GJ33" t="s">
         <v>212</v>
@@ -22354,7 +22372,7 @@
         <v>212</v>
       </c>
       <c r="GI34" s="2" t="s">
-        <v>3228</v>
+        <v>3230</v>
       </c>
       <c r="GJ34" t="s">
         <v>212</v>
@@ -22524,7 +22542,7 @@
         <v>212</v>
       </c>
       <c r="GI35" s="2" t="s">
-        <v>3229</v>
+        <v>3231</v>
       </c>
       <c r="GJ35" t="s">
         <v>212</v>
@@ -22694,7 +22712,7 @@
         <v>212</v>
       </c>
       <c r="GI36" s="2" t="s">
-        <v>3230</v>
+        <v>3232</v>
       </c>
       <c r="GJ36" t="s">
         <v>212</v>
@@ -22864,7 +22882,7 @@
         <v>212</v>
       </c>
       <c r="GI37" s="2" t="s">
-        <v>3231</v>
+        <v>3233</v>
       </c>
       <c r="GJ37" t="s">
         <v>212</v>
@@ -23034,7 +23052,7 @@
         <v>212</v>
       </c>
       <c r="GI38" s="2" t="s">
-        <v>3232</v>
+        <v>3234</v>
       </c>
       <c r="GJ38" t="s">
         <v>212</v>
@@ -23204,7 +23222,7 @@
         <v>212</v>
       </c>
       <c r="GI39" s="2" t="s">
-        <v>3233</v>
+        <v>3235</v>
       </c>
       <c r="GJ39" t="s">
         <v>212</v>
@@ -23374,7 +23392,7 @@
         <v>212</v>
       </c>
       <c r="GI40" s="2" t="s">
-        <v>3234</v>
+        <v>3236</v>
       </c>
       <c r="GJ40" t="s">
         <v>212</v>
@@ -59676,113 +59694,113 @@
     <hyperlink ref="GG12" r:id="rId32"/>
     <hyperlink ref="GI12" r:id="rId33"/>
     <hyperlink ref="GE13" r:id="rId34"/>
-    <hyperlink ref="GI13" r:id="rId35"/>
-    <hyperlink ref="GE14" r:id="rId36"/>
-    <hyperlink ref="GI14" r:id="rId37"/>
-    <hyperlink ref="GE15" r:id="rId38"/>
-    <hyperlink ref="GI15" r:id="rId39"/>
-    <hyperlink ref="GE16" r:id="rId40"/>
-    <hyperlink ref="GI16" r:id="rId41"/>
-    <hyperlink ref="GE17" r:id="rId42"/>
-    <hyperlink ref="GI17" r:id="rId43"/>
-    <hyperlink ref="GE18" r:id="rId44"/>
-    <hyperlink ref="GI18" r:id="rId45"/>
-    <hyperlink ref="GE19" r:id="rId46"/>
-    <hyperlink ref="GI19" r:id="rId47"/>
-    <hyperlink ref="GE20" r:id="rId48"/>
-    <hyperlink ref="GI20" r:id="rId49"/>
-    <hyperlink ref="GE21" r:id="rId50"/>
-    <hyperlink ref="GI21" r:id="rId51"/>
-    <hyperlink ref="GE22" r:id="rId52"/>
-    <hyperlink ref="GI22" r:id="rId53"/>
-    <hyperlink ref="GE23" r:id="rId54"/>
-    <hyperlink ref="GI23" r:id="rId55"/>
-    <hyperlink ref="GE24" r:id="rId56"/>
-    <hyperlink ref="GI24" r:id="rId57"/>
-    <hyperlink ref="GE25" r:id="rId58"/>
-    <hyperlink ref="GI25" r:id="rId59"/>
-    <hyperlink ref="GE26" r:id="rId60"/>
-    <hyperlink ref="GI26" r:id="rId61"/>
-    <hyperlink ref="GE27" r:id="rId62"/>
-    <hyperlink ref="GI27" r:id="rId63"/>
-    <hyperlink ref="GE28" r:id="rId64"/>
-    <hyperlink ref="GI28" r:id="rId65"/>
-    <hyperlink ref="GE29" r:id="rId66"/>
-    <hyperlink ref="GI29" r:id="rId67"/>
-    <hyperlink ref="GE30" r:id="rId68"/>
-    <hyperlink ref="GI30" r:id="rId69"/>
-    <hyperlink ref="GE31" r:id="rId70"/>
-    <hyperlink ref="GI31" r:id="rId71"/>
-    <hyperlink ref="GE32" r:id="rId72"/>
-    <hyperlink ref="GI32" r:id="rId73"/>
-    <hyperlink ref="GE33" r:id="rId74"/>
-    <hyperlink ref="GI33" r:id="rId75"/>
-    <hyperlink ref="GE34" r:id="rId76"/>
-    <hyperlink ref="GI34" r:id="rId77"/>
-    <hyperlink ref="GE35" r:id="rId78"/>
-    <hyperlink ref="GI35" r:id="rId79"/>
-    <hyperlink ref="GE36" r:id="rId80"/>
-    <hyperlink ref="GI36" r:id="rId81"/>
-    <hyperlink ref="GE37" r:id="rId82"/>
-    <hyperlink ref="GI37" r:id="rId83"/>
-    <hyperlink ref="GE38" r:id="rId84"/>
-    <hyperlink ref="GI38" r:id="rId85"/>
-    <hyperlink ref="GE39" r:id="rId86"/>
-    <hyperlink ref="GI39" r:id="rId87"/>
-    <hyperlink ref="GE40" r:id="rId88"/>
-    <hyperlink ref="GI40" r:id="rId89"/>
-    <hyperlink ref="GE41" r:id="rId90"/>
-    <hyperlink ref="GE42" r:id="rId91"/>
-    <hyperlink ref="GE43" r:id="rId92"/>
-    <hyperlink ref="GE44" r:id="rId93"/>
-    <hyperlink ref="GE45" r:id="rId94"/>
-    <hyperlink ref="GE46" r:id="rId95"/>
-    <hyperlink ref="GE47" r:id="rId96"/>
-    <hyperlink ref="GE48" r:id="rId97"/>
-    <hyperlink ref="GE49" r:id="rId98"/>
-    <hyperlink ref="GE50" r:id="rId99"/>
-    <hyperlink ref="GE51" r:id="rId100"/>
-    <hyperlink ref="GE52" r:id="rId101"/>
-    <hyperlink ref="GE53" r:id="rId102"/>
-    <hyperlink ref="GE54" r:id="rId103"/>
-    <hyperlink ref="GE55" r:id="rId104"/>
-    <hyperlink ref="GE56" r:id="rId105"/>
-    <hyperlink ref="GE57" r:id="rId106"/>
-    <hyperlink ref="GE58" r:id="rId107"/>
-    <hyperlink ref="GE59" r:id="rId108"/>
-    <hyperlink ref="GE60" r:id="rId109"/>
-    <hyperlink ref="GE61" r:id="rId110"/>
-    <hyperlink ref="GE62" r:id="rId111"/>
-    <hyperlink ref="GE63" r:id="rId112"/>
-    <hyperlink ref="GE64" r:id="rId113"/>
-    <hyperlink ref="GE65" r:id="rId114"/>
-    <hyperlink ref="GE66" r:id="rId115"/>
-    <hyperlink ref="GE67" r:id="rId116"/>
-    <hyperlink ref="GE68" r:id="rId117"/>
-    <hyperlink ref="GE69" r:id="rId118"/>
-    <hyperlink ref="GE70" r:id="rId119"/>
-    <hyperlink ref="GE71" r:id="rId120"/>
-    <hyperlink ref="GE72" r:id="rId121"/>
-    <hyperlink ref="GE73" r:id="rId122"/>
-    <hyperlink ref="GE74" r:id="rId123"/>
-    <hyperlink ref="GE75" r:id="rId124"/>
-    <hyperlink ref="GE76" r:id="rId125"/>
-    <hyperlink ref="GE77" r:id="rId126"/>
-    <hyperlink ref="GE78" r:id="rId127"/>
-    <hyperlink ref="GE79" r:id="rId128"/>
-    <hyperlink ref="GE80" r:id="rId129"/>
-    <hyperlink ref="GE81" r:id="rId130"/>
-    <hyperlink ref="GE82" r:id="rId131"/>
-    <hyperlink ref="GE83" r:id="rId132"/>
-    <hyperlink ref="GE84" r:id="rId133"/>
-    <hyperlink ref="GE85" r:id="rId134"/>
-    <hyperlink ref="GE86" r:id="rId135"/>
-    <hyperlink ref="GE87" r:id="rId136"/>
+    <hyperlink ref="GG13" r:id="rId35"/>
+    <hyperlink ref="GI13" r:id="rId36"/>
+    <hyperlink ref="GE14" r:id="rId37"/>
+    <hyperlink ref="GG14" r:id="rId38"/>
+    <hyperlink ref="GI14" r:id="rId39"/>
+    <hyperlink ref="GE15" r:id="rId40"/>
+    <hyperlink ref="GI15" r:id="rId41"/>
+    <hyperlink ref="GE16" r:id="rId42"/>
+    <hyperlink ref="GI16" r:id="rId43"/>
+    <hyperlink ref="GE17" r:id="rId44"/>
+    <hyperlink ref="GI17" r:id="rId45"/>
+    <hyperlink ref="GE18" r:id="rId46"/>
+    <hyperlink ref="GI18" r:id="rId47"/>
+    <hyperlink ref="GE19" r:id="rId48"/>
+    <hyperlink ref="GI19" r:id="rId49"/>
+    <hyperlink ref="GE20" r:id="rId50"/>
+    <hyperlink ref="GI20" r:id="rId51"/>
+    <hyperlink ref="GE21" r:id="rId52"/>
+    <hyperlink ref="GI21" r:id="rId53"/>
+    <hyperlink ref="GE22" r:id="rId54"/>
+    <hyperlink ref="GI22" r:id="rId55"/>
+    <hyperlink ref="GE23" r:id="rId56"/>
+    <hyperlink ref="GI23" r:id="rId57"/>
+    <hyperlink ref="GE24" r:id="rId58"/>
+    <hyperlink ref="GI24" r:id="rId59"/>
+    <hyperlink ref="GE25" r:id="rId60"/>
+    <hyperlink ref="GI25" r:id="rId61"/>
+    <hyperlink ref="GE26" r:id="rId62"/>
+    <hyperlink ref="GI26" r:id="rId63"/>
+    <hyperlink ref="GE27" r:id="rId64"/>
+    <hyperlink ref="GI27" r:id="rId65"/>
+    <hyperlink ref="GE28" r:id="rId66"/>
+    <hyperlink ref="GI28" r:id="rId67"/>
+    <hyperlink ref="GE29" r:id="rId68"/>
+    <hyperlink ref="GI29" r:id="rId69"/>
+    <hyperlink ref="GE30" r:id="rId70"/>
+    <hyperlink ref="GI30" r:id="rId71"/>
+    <hyperlink ref="GE31" r:id="rId72"/>
+    <hyperlink ref="GI31" r:id="rId73"/>
+    <hyperlink ref="GE32" r:id="rId74"/>
+    <hyperlink ref="GI32" r:id="rId75"/>
+    <hyperlink ref="GE33" r:id="rId76"/>
+    <hyperlink ref="GI33" r:id="rId77"/>
+    <hyperlink ref="GE34" r:id="rId78"/>
+    <hyperlink ref="GI34" r:id="rId79"/>
+    <hyperlink ref="GE35" r:id="rId80"/>
+    <hyperlink ref="GI35" r:id="rId81"/>
+    <hyperlink ref="GE36" r:id="rId82"/>
+    <hyperlink ref="GI36" r:id="rId83"/>
+    <hyperlink ref="GE37" r:id="rId84"/>
+    <hyperlink ref="GI37" r:id="rId85"/>
+    <hyperlink ref="GE38" r:id="rId86"/>
+    <hyperlink ref="GI38" r:id="rId87"/>
+    <hyperlink ref="GE39" r:id="rId88"/>
+    <hyperlink ref="GI39" r:id="rId89"/>
+    <hyperlink ref="GE40" r:id="rId90"/>
+    <hyperlink ref="GI40" r:id="rId91"/>
+    <hyperlink ref="GE41" r:id="rId92"/>
+    <hyperlink ref="GE42" r:id="rId93"/>
+    <hyperlink ref="GE43" r:id="rId94"/>
+    <hyperlink ref="GE44" r:id="rId95"/>
+    <hyperlink ref="GE45" r:id="rId96"/>
+    <hyperlink ref="GE46" r:id="rId97"/>
+    <hyperlink ref="GE47" r:id="rId98"/>
+    <hyperlink ref="GE48" r:id="rId99"/>
+    <hyperlink ref="GE49" r:id="rId100"/>
+    <hyperlink ref="GE50" r:id="rId101"/>
+    <hyperlink ref="GE51" r:id="rId102"/>
+    <hyperlink ref="GE52" r:id="rId103"/>
+    <hyperlink ref="GE53" r:id="rId104"/>
+    <hyperlink ref="GE54" r:id="rId105"/>
+    <hyperlink ref="GE55" r:id="rId106"/>
+    <hyperlink ref="GE56" r:id="rId107"/>
+    <hyperlink ref="GE57" r:id="rId108"/>
+    <hyperlink ref="GE58" r:id="rId109"/>
+    <hyperlink ref="GE59" r:id="rId110"/>
+    <hyperlink ref="GE60" r:id="rId111"/>
+    <hyperlink ref="GE61" r:id="rId112"/>
+    <hyperlink ref="GE62" r:id="rId113"/>
+    <hyperlink ref="GE63" r:id="rId114"/>
+    <hyperlink ref="GE64" r:id="rId115"/>
+    <hyperlink ref="GE65" r:id="rId116"/>
+    <hyperlink ref="GE66" r:id="rId117"/>
+    <hyperlink ref="GE67" r:id="rId118"/>
+    <hyperlink ref="GE68" r:id="rId119"/>
+    <hyperlink ref="GE69" r:id="rId120"/>
+    <hyperlink ref="GE70" r:id="rId121"/>
+    <hyperlink ref="GE71" r:id="rId122"/>
+    <hyperlink ref="GE72" r:id="rId123"/>
+    <hyperlink ref="GE73" r:id="rId124"/>
+    <hyperlink ref="GE74" r:id="rId125"/>
+    <hyperlink ref="GE75" r:id="rId126"/>
+    <hyperlink ref="GE76" r:id="rId127"/>
+    <hyperlink ref="GE77" r:id="rId128"/>
+    <hyperlink ref="GE78" r:id="rId129"/>
+    <hyperlink ref="GE79" r:id="rId130"/>
+    <hyperlink ref="GE80" r:id="rId131"/>
+    <hyperlink ref="GE81" r:id="rId132"/>
+    <hyperlink ref="GE82" r:id="rId133"/>
+    <hyperlink ref="GE83" r:id="rId134"/>
+    <hyperlink ref="GE84" r:id="rId135"/>
+    <hyperlink ref="GE85" r:id="rId136"/>
+    <hyperlink ref="GE86" r:id="rId137"/>
+    <hyperlink ref="GE87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="111">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -59892,6 +59910,8 @@
     <tablePart r:id="rId245"/>
     <tablePart r:id="rId246"/>
     <tablePart r:id="rId247"/>
+    <tablePart r:id="rId248"/>
+    <tablePart r:id="rId249"/>
   </tableParts>
 </worksheet>
 </file>
@@ -69321,7 +69341,7 @@
       <formula1>'Codelijsten'!$GE$4:$GE$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$GG$4:$GG$12</formula1>
+      <formula1>'Codelijsten'!$GG$4:$GG$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -69447,61 +69467,61 @@
   <sheetData>
     <row r="1" spans="1:78" hidden="1">
       <c r="A1" s="10" t="s">
-        <v>3239</v>
+        <v>3241</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>3240</v>
+        <v>3242</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>3242</v>
+        <v>3244</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>3243</v>
+        <v>3245</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>3244</v>
+        <v>3246</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3246</v>
+        <v>3248</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>3248</v>
+        <v>3250</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>3250</v>
+        <v>3252</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>3252</v>
+        <v>3254</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>3254</v>
+        <v>3256</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>3256</v>
+        <v>3258</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3257</v>
+        <v>3259</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>3258</v>
+        <v>3260</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>3259</v>
+        <v>3261</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>3263</v>
+        <v>3265</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>3266</v>
+        <v>3268</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>3267</v>
+        <v>3269</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>3268</v>
+        <v>3270</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>3034</v>
@@ -69516,16 +69536,16 @@
         <v>125</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>3272</v>
+        <v>3274</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>3273</v>
+        <v>3275</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>3274</v>
+        <v>3276</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>1528</v>
@@ -69558,76 +69578,76 @@
         <v>1446</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>3275</v>
+        <v>3277</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>3276</v>
+        <v>3278</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>3277</v>
+        <v>3279</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>3278</v>
+        <v>3280</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>3279</v>
+        <v>3281</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>3280</v>
+        <v>3282</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>3281</v>
+        <v>3283</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>3282</v>
+        <v>3284</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>3283</v>
+        <v>3285</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>3284</v>
+        <v>3286</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>3285</v>
+        <v>3287</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>3286</v>
+        <v>3288</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>3287</v>
+        <v>3289</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>3288</v>
+        <v>3290</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>3289</v>
+        <v>3291</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>3290</v>
+        <v>3292</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>3291</v>
+        <v>3293</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>3292</v>
+        <v>3294</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>3293</v>
+        <v>3295</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>3294</v>
+        <v>3296</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>3295</v>
+        <v>3297</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>3296</v>
+        <v>3298</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>3297</v>
+        <v>3299</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>3298</v>
+        <v>3300</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>181</v>
@@ -69810,7 +69830,7 @@
         <v>1440</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>3241</v>
+        <v>3243</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1442</v>
@@ -69819,7 +69839,7 @@
         <v>1444</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>3265</v>
+        <v>3267</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -69833,7 +69853,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8" t="s">
-        <v>3270</v>
+        <v>3272</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
@@ -69946,13 +69966,13 @@
     </row>
     <row r="4" spans="1:78" hidden="1">
       <c r="E4" s="8" t="s">
-        <v>3245</v>
+        <v>3247</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>3247</v>
+        <v>3249</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>3260</v>
+        <v>3262</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -69962,13 +69982,13 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="1" t="s">
-        <v>3262</v>
+        <v>3264</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>3264</v>
+        <v>3266</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>3269</v>
+        <v>3271</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -70089,16 +70109,16 @@
     </row>
     <row r="6" spans="1:78" hidden="1">
       <c r="G6" s="8" t="s">
-        <v>3249</v>
+        <v>3251</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>3251</v>
+        <v>3253</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>3253</v>
+        <v>3255</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>3255</v>
+        <v>3257</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>1490</v>
@@ -70115,61 +70135,61 @@
     </row>
     <row r="7" spans="1:78">
       <c r="A7" s="10" t="s">
-        <v>3239</v>
+        <v>3241</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>3240</v>
+        <v>3242</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>3242</v>
+        <v>3244</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3243</v>
+        <v>3245</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>3244</v>
+        <v>3246</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>3246</v>
+        <v>3248</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>3248</v>
+        <v>3250</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>3250</v>
+        <v>3252</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>3252</v>
+        <v>3254</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>3254</v>
+        <v>3256</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>3256</v>
+        <v>3258</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>3257</v>
+        <v>3259</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>3258</v>
+        <v>3260</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>3259</v>
+        <v>3261</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>3263</v>
+        <v>3265</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>3266</v>
+        <v>3268</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>3267</v>
+        <v>3269</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>3268</v>
+        <v>3270</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>3034</v>
@@ -70184,16 +70204,16 @@
         <v>125</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>3272</v>
+        <v>3274</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>3273</v>
+        <v>3275</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>3274</v>
+        <v>3276</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>1528</v>
@@ -70226,76 +70246,76 @@
         <v>1446</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>3275</v>
+        <v>3277</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>3276</v>
+        <v>3278</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>3277</v>
+        <v>3279</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>3278</v>
+        <v>3280</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>3279</v>
+        <v>3281</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>3280</v>
+        <v>3282</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>3281</v>
+        <v>3283</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>3282</v>
+        <v>3284</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>3283</v>
+        <v>3285</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>3284</v>
+        <v>3286</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>3285</v>
+        <v>3287</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>3286</v>
+        <v>3288</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>3287</v>
+        <v>3289</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>3288</v>
+        <v>3290</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>3289</v>
+        <v>3291</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>3290</v>
+        <v>3292</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>3291</v>
+        <v>3293</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>3292</v>
+        <v>3294</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>3293</v>
+        <v>3295</v>
       </c>
       <c r="BE7" s="1" t="s">
-        <v>3294</v>
+        <v>3296</v>
       </c>
       <c r="BF7" s="1" t="s">
-        <v>3295</v>
+        <v>3297</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>3296</v>
+        <v>3298</v>
       </c>
       <c r="BH7" s="1" t="s">
-        <v>3297</v>
+        <v>3299</v>
       </c>
       <c r="BI7" s="1" t="s">
-        <v>3298</v>
+        <v>3300</v>
       </c>
       <c r="BJ7" s="1" t="s">
         <v>181</v>
@@ -70475,16 +70495,16 @@
         <v>1288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3304</v>
+        <v>3306</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3306</v>
+        <v>3308</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3308</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="2" spans="1:7" hidden="1">
@@ -70496,7 +70516,7 @@
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="1" t="s">
-        <v>3310</v>
+        <v>3312</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -70510,16 +70530,16 @@
         <v>764</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>3303</v>
+        <v>3305</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>3305</v>
+        <v>3307</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3307</v>
+        <v>3309</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3309</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -70533,16 +70553,16 @@
         <v>1288</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>3304</v>
+        <v>3306</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3306</v>
+        <v>3308</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>3308</v>
+        <v>3310</v>
       </c>
     </row>
   </sheetData>
@@ -70575,50 +70595,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>3312</v>
+        <v>3314</v>
       </c>
       <c r="B1" t="s">
-        <v>3313</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3314</v>
+        <v>3316</v>
       </c>
       <c r="B2" t="s">
-        <v>3315</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3316</v>
+        <v>3318</v>
       </c>
       <c r="B3" t="s">
-        <v>3317</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3318</v>
+        <v>3320</v>
       </c>
       <c r="B4" t="s">
-        <v>3319</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3320</v>
+        <v>3322</v>
       </c>
       <c r="B5" t="s">
-        <v>3321</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3322</v>
+        <v>3324</v>
       </c>
       <c r="B6" t="s">
-        <v>3323</v>
+        <v>3325</v>
       </c>
     </row>
   </sheetData>

--- a/templates/oefen/oefen_grondwater_template_full.xlsx
+++ b/templates/oefen/oefen_grondwater_template_full.xlsx
@@ -9969,19 +9969,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:28.670708</t>
+    <t>2026-05-19 11:29:01.379385</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>

--- a/templates/oefen/oefen_grondwater_template_full.xlsx
+++ b/templates/oefen/oefen_grondwater_template_full.xlsx
@@ -9969,13 +9969,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:29:01.379385</t>
+    <t>2026-05-19 14:52:53.306717</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
